--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,6 +1550,148 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129433212</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karåforsens kraftstation, Karåforsens kraftstation, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>476791</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6580933</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>129433212</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>129433212</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>129433212</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>129433212</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>129433212</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112529425</v>
+        <v>112529410</v>
       </c>
       <c r="B2" t="n">
-        <v>99050</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476566</v>
+        <v>476545</v>
       </c>
       <c r="R2" t="n">
-        <v>6580570</v>
+        <v>6580485</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112529423</v>
+        <v>112529426</v>
       </c>
       <c r="B3" t="n">
-        <v>89920</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1964</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Flavidoporia mellita</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttillä) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476575</v>
+        <v>476552</v>
       </c>
       <c r="R3" t="n">
-        <v>6580579</v>
+        <v>6580466</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,7 +865,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>sälglåga</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -892,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112529422</v>
+        <v>112529416</v>
       </c>
       <c r="B4" t="n">
-        <v>93343</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>241</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476588</v>
+        <v>476543</v>
       </c>
       <c r="R4" t="n">
-        <v>6580603</v>
+        <v>6580572</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,37 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112529427</v>
+        <v>112529424</v>
       </c>
       <c r="B5" t="n">
-        <v>90407</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476550</v>
+        <v>476556</v>
       </c>
       <c r="R5" t="n">
-        <v>6580466</v>
+        <v>6580563</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,7 +1072,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>alved</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1109,37 +1094,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112529428</v>
+        <v>112529427</v>
       </c>
       <c r="B6" t="n">
-        <v>89482</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>253774</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljungporing</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sistotrema albopallescens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476562</v>
+        <v>476550</v>
       </c>
       <c r="R6" t="n">
-        <v>6580434</v>
+        <v>6580466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1178,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>gråalsved</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,37 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112529426</v>
+        <v>112529421</v>
       </c>
       <c r="B7" t="n">
-        <v>89921</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>662</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Pälsfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Frullania austinii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476552</v>
+        <v>476578</v>
       </c>
       <c r="R7" t="n">
-        <v>6580466</v>
+        <v>6580632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1309,7 +1284,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1331,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113381849</v>
+        <v>113381839</v>
       </c>
       <c r="B8" t="n">
-        <v>96286</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,12 +1326,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania bolanderi</t>
+          <t>Frullania austinii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476573</v>
+        <v>476566</v>
       </c>
       <c r="R8" t="n">
-        <v>6580618</v>
+        <v>6580656</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,37 +1412,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113381917</v>
+        <v>113381844</v>
       </c>
       <c r="B9" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Pälsfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania austinii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476604</v>
+        <v>476568</v>
       </c>
       <c r="R9" t="n">
-        <v>6580612</v>
+        <v>6580655</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1531,7 +1496,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>granstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1553,53 +1518,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129433212</v>
+        <v>113381845</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>97788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Pälsfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania austinii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karåforsens kraftstation, Karåforsens kraftstation, Vrm</t>
+          <t>Karåsforsen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476791</v>
+        <v>476567</v>
       </c>
       <c r="R10" t="n">
-        <v>6580933</v>
+        <v>6580658</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,27 +1583,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hack i död gran</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,43 +1600,2686 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113381846</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>662</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>476571</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6580648</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113381847</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>662</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476575</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6580640</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113381848</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>662</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476569</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6580642</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113381849</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>662</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>476573</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6580618</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113381850</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>662</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476571</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6580638</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113381851</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>662</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476570</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6580632</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113381852</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>662</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pälsfrullania</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Frullania austinii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>J.J.Atwood, Vilnet, Mamontov &amp; Konstant</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>476571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6580625</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112529437</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92323</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>715</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gloeoporus pannocinctus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Romell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476582</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6580419</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112529414</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96460</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt spretmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Herzogiella turfacea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Lindb.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>476534</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6580554</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112529412</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97449</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>990</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Liten hornflikmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophozia ascendens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>476539</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6580574</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>372605</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100856</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1256</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Storgröe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poa remota</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Karåsens kraftverk, ca 50 m N krafverkets utlopp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>476606</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6580747</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Kar-0133</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2009-05-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2009-05-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Omgivande skog gallrades kraftigt vintern 2009</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Fuktigt - vått dike vid körväg</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112529423</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92201</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Honungsticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fomitopsis mellita</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>476574</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6580579</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>sälglåga</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112529436</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2404</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dvärgkällmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Philonotis capillaris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>476576</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6580422</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112529435</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97796</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>476558</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6580403</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112529433</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>476558</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6580403</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112529429</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>476569</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6580424</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112529434</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>476560</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6580413</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112529430</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96450</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2675</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Piskbaronmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pseudanomodon attenuatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ignatov &amp; Fedosov</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>476569</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6580424</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112529422</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>476588</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6580603</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>112529415</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96459</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2819</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Trind spretmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Herzogiella striatella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>476534</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6580554</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113381917</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>476604</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6580612</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>granstubbe</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129433212</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Karåforsens kraftstation, Karåforsens kraftstation, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>476791</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6580933</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Per Arneborn</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Per Arneborn</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>112529425</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>476567</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6580570</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>112529428</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91718</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>253774</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ljungporing</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sistotrema albopallescens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>476562</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6580434</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>gråalsved</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>112529419</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Karåsforsen, Svartälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>476551</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6580628</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53025-2025 artfynd.xlsx
+++ b/artfynd/A 53025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529416</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529427</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529421</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381839</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381845</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381846</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381847</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381848</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2040,6 +2105,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381849</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381850</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2252,6 +2327,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381851</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381852</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529437</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529414</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2661,6 +2756,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529412</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2791,6 +2891,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/372605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2897,6 +3002,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529423</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2998,6 +3108,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529436</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3099,6 +3214,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529435</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529433</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3301,6 +3426,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529429</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3402,6 +3532,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529434</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3508,6 +3643,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529430</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3609,6 +3749,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529422</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3715,6 +3860,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529415</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3821,6 +3971,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381917</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3963,6 +4118,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129433212</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4064,6 +4224,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529425</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4168,6 +4333,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529428</t>
         </is>
       </c>
     </row>
@@ -4280,8 +4450,49 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>